--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C18456F-6118-464E-B75B-118D7ABFB611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B80541EA-64FF-4209-9DEA-1C1C8B019E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,7 +1248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421894DB-181F-4719-89EA-2626078D6AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD1E007-1AB1-45C5-B3D6-2341FA16FAD3}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1305,7 +1305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB587594-767A-4FF9-8003-BFF69B595E7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F45C14-D874-4A8C-B02E-443108FC8F82}">
   <dimension ref="B9:O30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2007,7 +2007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{284C9875-0469-4380-BF9B-766209217F97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E59ACBE-AEC4-493B-BB3F-DB0F4BE97DEA}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3590,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC6E70F-E192-445D-B995-7826AE32FA8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694F1164-4E00-4151-B243-FE745E710CAF}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3634,7 +3634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB08D314-5A31-4CC7-928E-62889A256C8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D01F8DC-197A-4393-B296-153C86D4B1CC}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3683,7 +3683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6248EF-72C1-4E47-A6C9-DC4FB1508181}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE2D41E2-B166-4833-9A78-5DBAF2524B30}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3721,7 +3721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C194B81F-08ED-4BC4-AB38-E41D1EE52DEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010BCA31-C76F-42B6-BC14-B18B2645E9C3}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3823,7 +3823,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>0.25275833333333331</v>
+        <v>0.25275833333333336</v>
       </c>
       <c r="E16" t="s">
         <v>167</v>
@@ -3879,7 +3879,7 @@
         <v>37</v>
       </c>
       <c r="D20">
-        <v>0.26399166666666668</v>
+        <v>0.26399166666666662</v>
       </c>
       <c r="E20" t="s">
         <v>167</v>
@@ -3893,7 +3893,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.27348333333333336</v>
+        <v>0.2734833333333333</v>
       </c>
       <c r="E21" t="s">
         <v>167</v>
@@ -3977,7 +3977,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.28628333333333328</v>
+        <v>0.28628333333333333</v>
       </c>
       <c r="E27" t="s">
         <v>167</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.26837499999999997</v>
+        <v>0.26837500000000003</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.24309166666666662</v>
+        <v>0.24309166666666668</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
@@ -4075,7 +4075,7 @@
         <v>37</v>
       </c>
       <c r="D34">
-        <v>0.24636666666666665</v>
+        <v>0.24636666666666671</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
@@ -4117,7 +4117,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.26184166666666669</v>
+        <v>0.26184166666666658</v>
       </c>
       <c r="E37" t="s">
         <v>167</v>
